--- a/testcase.calculator.xlsx
+++ b/testcase.calculator.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="96">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -283,19 +283,7 @@
     <t>Test the Fuctionality of Windows Calculator Application</t>
   </si>
   <si>
-    <t>Open the Calculator Application</t>
-  </si>
-  <si>
-    <t>Display show the result 7</t>
-  </si>
-  <si>
     <t>Test entire fuctionality of Calculator Application.</t>
-  </si>
-  <si>
-    <t>Display show the result 4</t>
-  </si>
-  <si>
-    <t>Display show the result 12</t>
   </si>
   <si>
     <t>Division By Zero (7/0)=</t>
@@ -313,25 +301,13 @@
     <t>Addition Operation(3+4)=</t>
   </si>
   <si>
-    <t>Display error</t>
-  </si>
-  <si>
     <t>Decimal Addition(2.5+2.5)=</t>
   </si>
   <si>
     <t>Clear © Button</t>
   </si>
   <si>
-    <t>Display show the result 5.0</t>
-  </si>
-  <si>
-    <t>Display show the result 15.0</t>
-  </si>
-  <si>
     <t>Decimal Multiplication(5.0*3)=</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Display resets to 0 </t>
   </si>
   <si>
     <t>Enter 2+3*4</t>
@@ -340,31 +316,19 @@
     <t>Enter 1 2 3,press backspace</t>
   </si>
   <si>
-    <t>Last digit should be removed and show 12</t>
-  </si>
-  <si>
     <t>Enter 50%</t>
   </si>
   <si>
     <t>Enter 888888*888888</t>
   </si>
   <si>
-    <t>Calculator should give correct large result or error if limit exceeded</t>
-  </si>
-  <si>
     <t xml:space="preserve">Any Calculation </t>
-  </si>
-  <si>
-    <t>Result should display instantly(&lt;1sec)</t>
   </si>
   <si>
     <t>Enter 3+1=then*3</t>
   </si>
   <si>
     <t>Enter 0+0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Result should be 0 </t>
   </si>
   <si>
     <t xml:space="preserve">Click on Minimuze Button </t>
@@ -380,37 +344,70 @@
 (-4+8)=</t>
   </si>
   <si>
-    <t>Application close without error</t>
-  </si>
-  <si>
     <t>Windows OS</t>
   </si>
   <si>
     <t>Calculator Application</t>
   </si>
   <si>
-    <t xml:space="preserve">Calculator launched successfully </t>
+    <t>Gauri Mahalle</t>
   </si>
   <si>
-    <t>Result should be 14 (not 20)</t>
+    <t>Open the Calculator Application.</t>
   </si>
   <si>
-    <t>Result should be 0.5(depending on implementation)</t>
+    <t>Calculator launched successfully.</t>
   </si>
   <si>
-    <t>First Result 4, then final result 12</t>
+    <t>Display show the result 7.</t>
   </si>
   <si>
-    <t xml:space="preserve">Calculator application should minimize </t>
+    <t>Display show the result 4.</t>
   </si>
   <si>
-    <t>Display shows the result 4</t>
+    <t>Display show the result 12.</t>
   </si>
   <si>
-    <t xml:space="preserve">Display show the result 0 </t>
+    <t>Display error.</t>
   </si>
   <si>
-    <t>Gauri Mahalle</t>
+    <t>Display show the result 5.0.</t>
+  </si>
+  <si>
+    <t>Display show the result 15.0.</t>
+  </si>
+  <si>
+    <t>Display resets to 0.</t>
+  </si>
+  <si>
+    <t>Result should be 14 (not 20).</t>
+  </si>
+  <si>
+    <t>Last digit should be removed and show 12.</t>
+  </si>
+  <si>
+    <t>Result should be 0.5(depending on implementation).</t>
+  </si>
+  <si>
+    <t>Calculator should give correct large result or error if limit exceeded.</t>
+  </si>
+  <si>
+    <t>Result should display instantly(&lt;1sec).</t>
+  </si>
+  <si>
+    <t>First Result 4, then final result 12.</t>
+  </si>
+  <si>
+    <t>Calculator application should minimize.</t>
+  </si>
+  <si>
+    <t>Display shows the result 4.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Display show the result 0. </t>
+  </si>
+  <si>
+    <t>Application close without error.</t>
   </si>
 </sst>
 </file>
@@ -420,7 +417,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mmmm\ d&quot;, &quot;yyyy"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -465,6 +462,26 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -883,7 +900,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -908,9 +925,6 @@
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -958,9 +972,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -972,29 +983,40 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1042,11 +1064,30 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1056,27 +1097,7 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1354,10 +1375,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="16.5" customHeight="1">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="52"/>
+      <c r="B1" s="53"/>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1365,13 +1386,13 @@
         <v>2</v>
       </c>
       <c r="E1" s="3"/>
-      <c r="F1" s="57" t="s">
+      <c r="F1" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="55"/>
       <c r="K1" s="4"/>
       <c r="L1" s="4"/>
       <c r="M1" s="4"/>
@@ -1389,10 +1410,10 @@
       <c r="Y1" s="4"/>
     </row>
     <row r="2" spans="1:25" ht="16.5" customHeight="1">
-      <c r="A2" s="58" t="s">
+      <c r="A2" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="42"/>
+      <c r="B2" s="43"/>
       <c r="C2" s="5" t="s">
         <v>5</v>
       </c>
@@ -1400,14 +1421,14 @@
         <v>6</v>
       </c>
       <c r="E2" s="7"/>
-      <c r="F2" s="40" t="s">
+      <c r="F2" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="42"/>
-      <c r="H2" s="59" t="s">
+      <c r="G2" s="43"/>
+      <c r="H2" s="60" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="42"/>
+      <c r="I2" s="43"/>
       <c r="J2" s="8" t="s">
         <v>9</v>
       </c>
@@ -1428,10 +1449,10 @@
       <c r="Y2" s="4"/>
     </row>
     <row r="3" spans="1:25" ht="25.5" customHeight="1">
-      <c r="A3" s="58" t="s">
+      <c r="A3" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="42"/>
+      <c r="B3" s="43"/>
       <c r="C3" s="5" t="s">
         <v>11</v>
       </c>
@@ -1439,15 +1460,15 @@
         <v>12</v>
       </c>
       <c r="E3" s="7"/>
-      <c r="F3" s="60">
+      <c r="F3" s="61">
         <v>46220</v>
       </c>
-      <c r="G3" s="42"/>
-      <c r="H3" s="59" t="s">
+      <c r="G3" s="43"/>
+      <c r="H3" s="60" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="42"/>
-      <c r="J3" s="10" t="s">
+      <c r="I3" s="43"/>
+      <c r="J3" s="9" t="s">
         <v>14</v>
       </c>
       <c r="K3" s="4"/>
@@ -1467,16 +1488,16 @@
       <c r="Y3" s="4"/>
     </row>
     <row r="4" spans="1:25" ht="16.5" customHeight="1">
-      <c r="A4" s="11"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
+      <c r="A4" s="10"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
-      <c r="J4" s="13"/>
+      <c r="J4" s="12"/>
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
@@ -1494,24 +1515,24 @@
       <c r="Y4" s="4"/>
     </row>
     <row r="5" spans="1:25" ht="16.5" customHeight="1">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="61" t="s">
+      <c r="B5" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="41"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="16" t="s">
+      <c r="C5" s="42"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="59" t="s">
+      <c r="G5" s="60" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="43"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="44"/>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
@@ -1529,24 +1550,24 @@
       <c r="Y5" s="4"/>
     </row>
     <row r="6" spans="1:25" ht="16.5" customHeight="1">
-      <c r="A6" s="17">
+      <c r="A6" s="16">
         <v>1</v>
       </c>
-      <c r="B6" s="40" t="s">
+      <c r="B6" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="41"/>
-      <c r="D6" s="42"/>
+      <c r="C6" s="42"/>
+      <c r="D6" s="43"/>
       <c r="E6" s="5"/>
-      <c r="F6" s="18">
+      <c r="F6" s="17">
         <v>1</v>
       </c>
-      <c r="G6" s="40" t="s">
+      <c r="G6" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="41"/>
-      <c r="I6" s="41"/>
-      <c r="J6" s="43"/>
+      <c r="H6" s="42"/>
+      <c r="I6" s="42"/>
+      <c r="J6" s="44"/>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
@@ -1564,24 +1585,24 @@
       <c r="Y6" s="4"/>
     </row>
     <row r="7" spans="1:25" ht="16.5" customHeight="1">
-      <c r="A7" s="17">
+      <c r="A7" s="16">
         <v>2</v>
       </c>
-      <c r="B7" s="40" t="s">
+      <c r="B7" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="41"/>
-      <c r="D7" s="42"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="43"/>
       <c r="E7" s="5"/>
-      <c r="F7" s="18">
+      <c r="F7" s="17">
         <v>2</v>
       </c>
-      <c r="G7" s="40" t="s">
+      <c r="G7" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="H7" s="41"/>
-      <c r="I7" s="41"/>
-      <c r="J7" s="43"/>
+      <c r="H7" s="42"/>
+      <c r="I7" s="42"/>
+      <c r="J7" s="44"/>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
@@ -1599,20 +1620,20 @@
       <c r="Y7" s="4"/>
     </row>
     <row r="8" spans="1:25" ht="16.5" customHeight="1">
-      <c r="A8" s="17">
+      <c r="A8" s="16">
         <v>3</v>
       </c>
-      <c r="B8" s="40"/>
-      <c r="C8" s="41"/>
-      <c r="D8" s="42"/>
+      <c r="B8" s="41"/>
+      <c r="C8" s="42"/>
+      <c r="D8" s="43"/>
       <c r="E8" s="5"/>
-      <c r="F8" s="18">
+      <c r="F8" s="17">
         <v>3</v>
       </c>
-      <c r="G8" s="40"/>
-      <c r="H8" s="41"/>
-      <c r="I8" s="41"/>
-      <c r="J8" s="43"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="42"/>
+      <c r="I8" s="42"/>
+      <c r="J8" s="44"/>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
@@ -1630,21 +1651,21 @@
       <c r="Y8" s="4"/>
     </row>
     <row r="9" spans="1:25" ht="16.5" customHeight="1">
-      <c r="A9" s="19">
+      <c r="A9" s="18">
         <v>4</v>
       </c>
-      <c r="B9" s="44"/>
-      <c r="C9" s="46"/>
-      <c r="D9" s="45"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="21">
+      <c r="B9" s="45"/>
+      <c r="C9" s="47"/>
+      <c r="D9" s="46"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="20">
         <v>4</v>
       </c>
-      <c r="G9" s="44"/>
-      <c r="H9" s="46"/>
-      <c r="I9" s="46"/>
-      <c r="J9" s="47"/>
-      <c r="K9" s="22"/>
+      <c r="G9" s="45"/>
+      <c r="H9" s="47"/>
+      <c r="I9" s="47"/>
+      <c r="J9" s="48"/>
+      <c r="K9" s="21"/>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
       <c r="N9" s="4"/>
@@ -1661,16 +1682,16 @@
       <c r="Y9" s="4"/>
     </row>
     <row r="10" spans="1:25" ht="12.75" customHeight="1">
-      <c r="A10" s="23"/>
-      <c r="B10" s="23"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="23"/>
-      <c r="F10" s="23"/>
-      <c r="G10" s="23"/>
-      <c r="H10" s="23"/>
-      <c r="I10" s="23"/>
-      <c r="J10" s="23"/>
+      <c r="A10" s="22"/>
+      <c r="B10" s="22"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="22"/>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
@@ -1688,20 +1709,20 @@
       <c r="Y10" s="4"/>
     </row>
     <row r="11" spans="1:25" ht="13.5" customHeight="1">
-      <c r="A11" s="24" t="s">
+      <c r="A11" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="48" t="s">
+      <c r="B11" s="49" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="49"/>
-      <c r="D11" s="49"/>
-      <c r="E11" s="49"/>
-      <c r="F11" s="49"/>
-      <c r="G11" s="49"/>
-      <c r="H11" s="49"/>
-      <c r="I11" s="49"/>
-      <c r="J11" s="49"/>
+      <c r="C11" s="50"/>
+      <c r="D11" s="50"/>
+      <c r="E11" s="50"/>
+      <c r="F11" s="50"/>
+      <c r="G11" s="50"/>
+      <c r="H11" s="50"/>
+      <c r="I11" s="50"/>
+      <c r="J11" s="50"/>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
@@ -1720,17 +1741,17 @@
     </row>
     <row r="12" spans="1:25" ht="13.5" customHeight="1">
       <c r="A12" s="4"/>
-      <c r="B12" s="50" t="s">
+      <c r="B12" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="49"/>
-      <c r="D12" s="49"/>
-      <c r="E12" s="49"/>
-      <c r="F12" s="49"/>
-      <c r="G12" s="49"/>
-      <c r="H12" s="49"/>
-      <c r="I12" s="49"/>
-      <c r="J12" s="49"/>
+      <c r="C12" s="50"/>
+      <c r="D12" s="50"/>
+      <c r="E12" s="50"/>
+      <c r="F12" s="50"/>
+      <c r="G12" s="50"/>
+      <c r="H12" s="50"/>
+      <c r="I12" s="50"/>
+      <c r="J12" s="50"/>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
@@ -1775,26 +1796,26 @@
       <c r="Y13" s="4"/>
     </row>
     <row r="14" spans="1:25" ht="12.75">
-      <c r="A14" s="27" t="s">
+      <c r="A14" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="51" t="s">
+      <c r="B14" s="52" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="52"/>
-      <c r="D14" s="51" t="s">
+      <c r="C14" s="53"/>
+      <c r="D14" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="E14" s="52"/>
-      <c r="F14" s="51" t="s">
+      <c r="E14" s="53"/>
+      <c r="F14" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="G14" s="53"/>
-      <c r="H14" s="52"/>
-      <c r="I14" s="51" t="s">
+      <c r="G14" s="54"/>
+      <c r="H14" s="53"/>
+      <c r="I14" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="J14" s="54"/>
+      <c r="J14" s="55"/>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
@@ -1812,26 +1833,26 @@
       <c r="Y14" s="4"/>
     </row>
     <row r="15" spans="1:25" ht="24.75" customHeight="1">
-      <c r="A15" s="17">
+      <c r="A15" s="16">
         <v>1</v>
       </c>
-      <c r="B15" s="55" t="s">
+      <c r="B15" s="56" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="42"/>
-      <c r="D15" s="40" t="s">
+      <c r="C15" s="43"/>
+      <c r="D15" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="E15" s="42"/>
-      <c r="F15" s="40" t="s">
+      <c r="E15" s="43"/>
+      <c r="F15" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="G15" s="41"/>
-      <c r="H15" s="42"/>
-      <c r="I15" s="40" t="s">
+      <c r="G15" s="42"/>
+      <c r="H15" s="43"/>
+      <c r="I15" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="J15" s="43"/>
+      <c r="J15" s="44"/>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
@@ -1849,26 +1870,26 @@
       <c r="Y15" s="4"/>
     </row>
     <row r="16" spans="1:25" ht="30.75" customHeight="1">
-      <c r="A16" s="17">
+      <c r="A16" s="16">
         <v>2</v>
       </c>
-      <c r="B16" s="40" t="s">
+      <c r="B16" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="42"/>
-      <c r="D16" s="40" t="s">
+      <c r="C16" s="43"/>
+      <c r="D16" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="42"/>
-      <c r="F16" s="40" t="s">
+      <c r="E16" s="43"/>
+      <c r="F16" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="G16" s="41"/>
-      <c r="H16" s="42"/>
-      <c r="I16" s="40" t="s">
+      <c r="G16" s="42"/>
+      <c r="H16" s="43"/>
+      <c r="I16" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="J16" s="43"/>
+      <c r="J16" s="44"/>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
@@ -1886,26 +1907,26 @@
       <c r="Y16" s="4"/>
     </row>
     <row r="17" spans="1:25" ht="12.75">
-      <c r="A17" s="17">
+      <c r="A17" s="16">
         <v>3</v>
       </c>
-      <c r="B17" s="40" t="s">
+      <c r="B17" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="42"/>
-      <c r="D17" s="40" t="s">
+      <c r="C17" s="43"/>
+      <c r="D17" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="E17" s="42"/>
-      <c r="F17" s="40" t="s">
+      <c r="E17" s="43"/>
+      <c r="F17" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="G17" s="41"/>
-      <c r="H17" s="42"/>
-      <c r="I17" s="40" t="s">
+      <c r="G17" s="42"/>
+      <c r="H17" s="43"/>
+      <c r="I17" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="J17" s="43"/>
+      <c r="J17" s="44"/>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
       <c r="M17" s="4"/>
@@ -1923,26 +1944,26 @@
       <c r="Y17" s="4"/>
     </row>
     <row r="18" spans="1:25" ht="12.75">
-      <c r="A18" s="17">
+      <c r="A18" s="16">
         <v>4</v>
       </c>
-      <c r="B18" s="40" t="s">
+      <c r="B18" s="41" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="42"/>
-      <c r="D18" s="40" t="s">
+      <c r="C18" s="43"/>
+      <c r="D18" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="E18" s="42"/>
-      <c r="F18" s="40" t="s">
+      <c r="E18" s="43"/>
+      <c r="F18" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="G18" s="41"/>
-      <c r="H18" s="42"/>
-      <c r="I18" s="40" t="s">
+      <c r="G18" s="42"/>
+      <c r="H18" s="43"/>
+      <c r="I18" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="J18" s="43"/>
+      <c r="J18" s="44"/>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
       <c r="M18" s="4"/>
@@ -1960,26 +1981,26 @@
       <c r="Y18" s="4"/>
     </row>
     <row r="19" spans="1:25" ht="12.75">
-      <c r="A19" s="28">
+      <c r="A19" s="26">
         <v>5</v>
       </c>
-      <c r="B19" s="40" t="s">
+      <c r="B19" s="41" t="s">
         <v>40</v>
       </c>
-      <c r="C19" s="42"/>
-      <c r="D19" s="40" t="s">
+      <c r="C19" s="43"/>
+      <c r="D19" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="E19" s="42"/>
-      <c r="F19" s="40" t="s">
+      <c r="E19" s="43"/>
+      <c r="F19" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="G19" s="41"/>
-      <c r="H19" s="42"/>
-      <c r="I19" s="40" t="s">
+      <c r="G19" s="42"/>
+      <c r="H19" s="43"/>
+      <c r="I19" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="J19" s="43"/>
+      <c r="J19" s="44"/>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
       <c r="M19" s="4"/>
@@ -1997,26 +2018,26 @@
       <c r="Y19" s="4"/>
     </row>
     <row r="20" spans="1:25" ht="12.75">
-      <c r="A20" s="28">
+      <c r="A20" s="26">
         <v>6</v>
       </c>
-      <c r="B20" s="40" t="s">
+      <c r="B20" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="C20" s="42"/>
-      <c r="D20" s="40" t="s">
+      <c r="C20" s="43"/>
+      <c r="D20" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="E20" s="42"/>
-      <c r="F20" s="40" t="s">
+      <c r="E20" s="43"/>
+      <c r="F20" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="G20" s="41"/>
-      <c r="H20" s="42"/>
-      <c r="I20" s="40" t="s">
+      <c r="G20" s="42"/>
+      <c r="H20" s="43"/>
+      <c r="I20" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="J20" s="43"/>
+      <c r="J20" s="44"/>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
       <c r="M20" s="4"/>
@@ -2034,26 +2055,26 @@
       <c r="Y20" s="4"/>
     </row>
     <row r="21" spans="1:25" ht="12.75">
-      <c r="A21" s="28">
+      <c r="A21" s="26">
         <v>7</v>
       </c>
-      <c r="B21" s="40" t="s">
+      <c r="B21" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="42"/>
-      <c r="D21" s="40" t="s">
+      <c r="C21" s="43"/>
+      <c r="D21" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="E21" s="42"/>
-      <c r="F21" s="40" t="s">
+      <c r="E21" s="43"/>
+      <c r="F21" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="G21" s="41"/>
-      <c r="H21" s="42"/>
-      <c r="I21" s="40" t="s">
+      <c r="G21" s="42"/>
+      <c r="H21" s="43"/>
+      <c r="I21" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="J21" s="43"/>
+      <c r="J21" s="44"/>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
       <c r="M21" s="4"/>
@@ -2071,26 +2092,26 @@
       <c r="Y21" s="4"/>
     </row>
     <row r="22" spans="1:25" ht="12.75">
-      <c r="A22" s="28">
+      <c r="A22" s="26">
         <v>8</v>
       </c>
-      <c r="B22" s="40" t="s">
+      <c r="B22" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="42"/>
-      <c r="D22" s="40" t="s">
+      <c r="C22" s="43"/>
+      <c r="D22" s="41" t="s">
         <v>45</v>
       </c>
-      <c r="E22" s="42"/>
-      <c r="F22" s="40" t="s">
+      <c r="E22" s="43"/>
+      <c r="F22" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="G22" s="41"/>
-      <c r="H22" s="42"/>
-      <c r="I22" s="40" t="s">
+      <c r="G22" s="42"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="J22" s="43"/>
+      <c r="J22" s="44"/>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
       <c r="M22" s="4"/>
@@ -2108,18 +2129,18 @@
       <c r="Y22" s="4"/>
     </row>
     <row r="23" spans="1:25" ht="12.75" customHeight="1">
-      <c r="A23" s="28">
+      <c r="A23" s="26">
         <v>9</v>
       </c>
-      <c r="B23" s="40"/>
-      <c r="C23" s="42"/>
-      <c r="D23" s="40"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="40"/>
-      <c r="G23" s="41"/>
-      <c r="H23" s="42"/>
-      <c r="I23" s="40"/>
-      <c r="J23" s="43"/>
+      <c r="B23" s="41"/>
+      <c r="C23" s="43"/>
+      <c r="D23" s="41"/>
+      <c r="E23" s="43"/>
+      <c r="F23" s="41"/>
+      <c r="G23" s="42"/>
+      <c r="H23" s="43"/>
+      <c r="I23" s="41"/>
+      <c r="J23" s="44"/>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
       <c r="M23" s="4"/>
@@ -2137,18 +2158,18 @@
       <c r="Y23" s="4"/>
     </row>
     <row r="24" spans="1:25" ht="12.75" customHeight="1">
-      <c r="A24" s="28">
+      <c r="A24" s="26">
         <v>10</v>
       </c>
-      <c r="B24" s="40"/>
-      <c r="C24" s="42"/>
-      <c r="D24" s="40"/>
-      <c r="E24" s="42"/>
-      <c r="F24" s="40"/>
-      <c r="G24" s="41"/>
-      <c r="H24" s="42"/>
-      <c r="I24" s="40"/>
-      <c r="J24" s="43"/>
+      <c r="B24" s="41"/>
+      <c r="C24" s="43"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="43"/>
+      <c r="F24" s="41"/>
+      <c r="G24" s="42"/>
+      <c r="H24" s="43"/>
+      <c r="I24" s="41"/>
+      <c r="J24" s="44"/>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
       <c r="M24" s="4"/>
@@ -2166,18 +2187,18 @@
       <c r="Y24" s="4"/>
     </row>
     <row r="25" spans="1:25" ht="12.75" customHeight="1">
-      <c r="A25" s="28">
+      <c r="A25" s="26">
         <v>11</v>
       </c>
-      <c r="B25" s="40"/>
-      <c r="C25" s="42"/>
-      <c r="D25" s="40"/>
-      <c r="E25" s="42"/>
-      <c r="F25" s="40"/>
-      <c r="G25" s="41"/>
-      <c r="H25" s="42"/>
-      <c r="I25" s="40"/>
-      <c r="J25" s="43"/>
+      <c r="B25" s="41"/>
+      <c r="C25" s="43"/>
+      <c r="D25" s="41"/>
+      <c r="E25" s="43"/>
+      <c r="F25" s="41"/>
+      <c r="G25" s="42"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="41"/>
+      <c r="J25" s="44"/>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
       <c r="M25" s="4"/>
@@ -2195,18 +2216,18 @@
       <c r="Y25" s="4"/>
     </row>
     <row r="26" spans="1:25" ht="12.75" customHeight="1">
-      <c r="A26" s="28">
+      <c r="A26" s="26">
         <v>12</v>
       </c>
-      <c r="B26" s="40"/>
-      <c r="C26" s="42"/>
-      <c r="D26" s="40"/>
-      <c r="E26" s="42"/>
-      <c r="F26" s="40"/>
-      <c r="G26" s="41"/>
-      <c r="H26" s="42"/>
-      <c r="I26" s="40"/>
-      <c r="J26" s="43"/>
+      <c r="B26" s="41"/>
+      <c r="C26" s="43"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="43"/>
+      <c r="F26" s="41"/>
+      <c r="G26" s="42"/>
+      <c r="H26" s="43"/>
+      <c r="I26" s="41"/>
+      <c r="J26" s="44"/>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
       <c r="M26" s="4"/>
@@ -2224,18 +2245,18 @@
       <c r="Y26" s="4"/>
     </row>
     <row r="27" spans="1:25" ht="12.75" customHeight="1">
-      <c r="A27" s="28">
+      <c r="A27" s="26">
         <v>13</v>
       </c>
-      <c r="B27" s="40"/>
-      <c r="C27" s="42"/>
-      <c r="D27" s="40"/>
-      <c r="E27" s="42"/>
-      <c r="F27" s="40"/>
-      <c r="G27" s="41"/>
-      <c r="H27" s="42"/>
-      <c r="I27" s="40"/>
-      <c r="J27" s="43"/>
+      <c r="B27" s="41"/>
+      <c r="C27" s="43"/>
+      <c r="D27" s="41"/>
+      <c r="E27" s="43"/>
+      <c r="F27" s="41"/>
+      <c r="G27" s="42"/>
+      <c r="H27" s="43"/>
+      <c r="I27" s="41"/>
+      <c r="J27" s="44"/>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
       <c r="M27" s="4"/>
@@ -2253,18 +2274,18 @@
       <c r="Y27" s="4"/>
     </row>
     <row r="28" spans="1:25" ht="12.75" customHeight="1">
-      <c r="A28" s="28">
+      <c r="A28" s="26">
         <v>14</v>
       </c>
-      <c r="B28" s="40"/>
-      <c r="C28" s="42"/>
-      <c r="D28" s="40"/>
-      <c r="E28" s="42"/>
-      <c r="F28" s="40"/>
-      <c r="G28" s="41"/>
-      <c r="H28" s="42"/>
-      <c r="I28" s="40"/>
-      <c r="J28" s="43"/>
+      <c r="B28" s="41"/>
+      <c r="C28" s="43"/>
+      <c r="D28" s="41"/>
+      <c r="E28" s="43"/>
+      <c r="F28" s="41"/>
+      <c r="G28" s="42"/>
+      <c r="H28" s="43"/>
+      <c r="I28" s="41"/>
+      <c r="J28" s="44"/>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
       <c r="M28" s="4"/>
@@ -2282,18 +2303,18 @@
       <c r="Y28" s="4"/>
     </row>
     <row r="29" spans="1:25" ht="12.75" customHeight="1">
-      <c r="A29" s="28">
+      <c r="A29" s="26">
         <v>15</v>
       </c>
-      <c r="B29" s="40"/>
-      <c r="C29" s="42"/>
-      <c r="D29" s="40"/>
-      <c r="E29" s="42"/>
-      <c r="F29" s="40"/>
-      <c r="G29" s="41"/>
-      <c r="H29" s="42"/>
-      <c r="I29" s="40"/>
-      <c r="J29" s="43"/>
+      <c r="B29" s="41"/>
+      <c r="C29" s="43"/>
+      <c r="D29" s="41"/>
+      <c r="E29" s="43"/>
+      <c r="F29" s="41"/>
+      <c r="G29" s="42"/>
+      <c r="H29" s="43"/>
+      <c r="I29" s="41"/>
+      <c r="J29" s="44"/>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
       <c r="M29" s="4"/>
@@ -2311,18 +2332,18 @@
       <c r="Y29" s="4"/>
     </row>
     <row r="30" spans="1:25" ht="12.75" customHeight="1">
-      <c r="A30" s="28">
+      <c r="A30" s="26">
         <v>16</v>
       </c>
-      <c r="B30" s="40"/>
-      <c r="C30" s="42"/>
-      <c r="D30" s="40"/>
-      <c r="E30" s="42"/>
-      <c r="F30" s="40"/>
-      <c r="G30" s="41"/>
-      <c r="H30" s="42"/>
-      <c r="I30" s="40"/>
-      <c r="J30" s="43"/>
+      <c r="B30" s="41"/>
+      <c r="C30" s="43"/>
+      <c r="D30" s="41"/>
+      <c r="E30" s="43"/>
+      <c r="F30" s="41"/>
+      <c r="G30" s="42"/>
+      <c r="H30" s="43"/>
+      <c r="I30" s="41"/>
+      <c r="J30" s="44"/>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
       <c r="M30" s="4"/>
@@ -2340,18 +2361,18 @@
       <c r="Y30" s="4"/>
     </row>
     <row r="31" spans="1:25" ht="12.75" customHeight="1">
-      <c r="A31" s="28">
+      <c r="A31" s="26">
         <v>17</v>
       </c>
-      <c r="B31" s="40"/>
-      <c r="C31" s="42"/>
-      <c r="D31" s="40"/>
-      <c r="E31" s="42"/>
-      <c r="F31" s="40"/>
-      <c r="G31" s="41"/>
-      <c r="H31" s="42"/>
-      <c r="I31" s="40"/>
-      <c r="J31" s="43"/>
+      <c r="B31" s="41"/>
+      <c r="C31" s="43"/>
+      <c r="D31" s="41"/>
+      <c r="E31" s="43"/>
+      <c r="F31" s="41"/>
+      <c r="G31" s="42"/>
+      <c r="H31" s="43"/>
+      <c r="I31" s="41"/>
+      <c r="J31" s="44"/>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
       <c r="M31" s="4"/>
@@ -2369,18 +2390,18 @@
       <c r="Y31" s="4"/>
     </row>
     <row r="32" spans="1:25" ht="12.75" customHeight="1">
-      <c r="A32" s="28">
+      <c r="A32" s="26">
         <v>18</v>
       </c>
-      <c r="B32" s="40"/>
-      <c r="C32" s="42"/>
-      <c r="D32" s="40"/>
-      <c r="E32" s="42"/>
-      <c r="F32" s="40"/>
-      <c r="G32" s="41"/>
-      <c r="H32" s="42"/>
-      <c r="I32" s="40"/>
-      <c r="J32" s="43"/>
+      <c r="B32" s="41"/>
+      <c r="C32" s="43"/>
+      <c r="D32" s="41"/>
+      <c r="E32" s="43"/>
+      <c r="F32" s="41"/>
+      <c r="G32" s="42"/>
+      <c r="H32" s="43"/>
+      <c r="I32" s="41"/>
+      <c r="J32" s="44"/>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
       <c r="M32" s="4"/>
@@ -2398,18 +2419,18 @@
       <c r="Y32" s="4"/>
     </row>
     <row r="33" spans="1:25" ht="12.75" customHeight="1">
-      <c r="A33" s="28">
+      <c r="A33" s="26">
         <v>19</v>
       </c>
-      <c r="B33" s="40"/>
-      <c r="C33" s="42"/>
-      <c r="D33" s="40"/>
-      <c r="E33" s="42"/>
-      <c r="F33" s="40"/>
-      <c r="G33" s="41"/>
-      <c r="H33" s="42"/>
-      <c r="I33" s="40"/>
-      <c r="J33" s="43"/>
+      <c r="B33" s="41"/>
+      <c r="C33" s="43"/>
+      <c r="D33" s="41"/>
+      <c r="E33" s="43"/>
+      <c r="F33" s="41"/>
+      <c r="G33" s="42"/>
+      <c r="H33" s="43"/>
+      <c r="I33" s="41"/>
+      <c r="J33" s="44"/>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
       <c r="M33" s="4"/>
@@ -2427,18 +2448,18 @@
       <c r="Y33" s="4"/>
     </row>
     <row r="34" spans="1:25" ht="12.75" customHeight="1">
-      <c r="A34" s="29">
+      <c r="A34" s="27">
         <v>20</v>
       </c>
-      <c r="B34" s="44"/>
-      <c r="C34" s="45"/>
-      <c r="D34" s="44"/>
-      <c r="E34" s="45"/>
-      <c r="F34" s="44"/>
-      <c r="G34" s="46"/>
-      <c r="H34" s="45"/>
-      <c r="I34" s="44"/>
-      <c r="J34" s="47"/>
+      <c r="B34" s="45"/>
+      <c r="C34" s="46"/>
+      <c r="D34" s="45"/>
+      <c r="E34" s="46"/>
+      <c r="F34" s="45"/>
+      <c r="G34" s="47"/>
+      <c r="H34" s="46"/>
+      <c r="I34" s="45"/>
+      <c r="J34" s="48"/>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
       <c r="M34" s="4"/>
@@ -28495,734 +28516,734 @@
   <dimension ref="A1:K43"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.140625" customWidth="1"/>
     <col min="3" max="3" width="16.5703125" customWidth="1"/>
     <col min="4" max="5" width="15.42578125" customWidth="1"/>
     <col min="6" max="6" width="5.7109375" customWidth="1"/>
     <col min="8" max="8" width="4.28515625" customWidth="1"/>
     <col min="9" max="9" width="15" customWidth="1"/>
-    <col min="10" max="10" width="7.28515625" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="56" t="s">
+    <row r="1" spans="1:10" ht="15">
+      <c r="A1" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="52"/>
+      <c r="B1" s="53"/>
       <c r="C1" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="3"/>
-      <c r="F1" s="57" t="s">
+      <c r="E1" s="34"/>
+      <c r="F1" s="58" t="s">
         <v>53</v>
       </c>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="54"/>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="58" t="s">
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="55"/>
+    </row>
+    <row r="2" spans="1:10" ht="15">
+      <c r="A2" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="30" t="s">
+      <c r="B2" s="43"/>
+      <c r="C2" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="7"/>
-      <c r="F2" s="40" t="s">
-        <v>96</v>
+      <c r="E2" s="36"/>
+      <c r="F2" s="41" t="s">
+        <v>76</v>
       </c>
-      <c r="G2" s="42"/>
-      <c r="H2" s="59" t="s">
+      <c r="G2" s="43"/>
+      <c r="H2" s="60" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="42"/>
-      <c r="J2" s="31" t="s">
+      <c r="I2" s="43"/>
+      <c r="J2" s="8" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="58" t="s">
+    <row r="3" spans="1:10" ht="15">
+      <c r="A3" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="42"/>
-      <c r="C3" s="30" t="s">
+      <c r="B3" s="43"/>
+      <c r="C3" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="7"/>
-      <c r="F3" s="74" t="s">
+      <c r="E3" s="36"/>
+      <c r="F3" s="61" t="s">
         <v>48</v>
       </c>
-      <c r="G3" s="42"/>
-      <c r="H3" s="59" t="s">
+      <c r="G3" s="43"/>
+      <c r="H3" s="60" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="42"/>
-      <c r="J3" s="32" t="s">
+      <c r="I3" s="43"/>
+      <c r="J3" s="9" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="11"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="13"/>
+    <row r="4" spans="1:10" ht="15">
+      <c r="A4" s="37"/>
+      <c r="B4" s="38"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="35"/>
+      <c r="J4" s="39"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="61" t="s">
+      <c r="B5" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="41"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="16" t="s">
+      <c r="C5" s="42"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="59" t="s">
+      <c r="G5" s="60" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="43"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="44"/>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="28">
+      <c r="A6" s="26">
         <v>1</v>
       </c>
-      <c r="B6" s="40" t="s">
+      <c r="B6" s="41" t="s">
+        <v>74</v>
+      </c>
+      <c r="C6" s="42"/>
+      <c r="D6" s="43"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="17">
+        <v>1</v>
+      </c>
+      <c r="G6" s="41" t="s">
+        <v>48</v>
+      </c>
+      <c r="H6" s="42"/>
+      <c r="I6" s="42"/>
+      <c r="J6" s="44"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="26">
+        <v>2</v>
+      </c>
+      <c r="B7" s="41" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="42"/>
+      <c r="D7" s="43"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="17">
+        <v>2</v>
+      </c>
+      <c r="G7" s="41" t="s">
+        <v>48</v>
+      </c>
+      <c r="H7" s="42"/>
+      <c r="I7" s="42"/>
+      <c r="J7" s="44"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="26">
+        <v>3</v>
+      </c>
+      <c r="B8" s="41"/>
+      <c r="C8" s="42"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="17">
+        <v>3</v>
+      </c>
+      <c r="G8" s="41"/>
+      <c r="H8" s="42"/>
+      <c r="I8" s="42"/>
+      <c r="J8" s="44"/>
+    </row>
+    <row r="9" spans="1:10" ht="13.5" thickBot="1">
+      <c r="A9" s="27">
+        <v>4</v>
+      </c>
+      <c r="B9" s="45"/>
+      <c r="C9" s="47"/>
+      <c r="D9" s="46"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="20">
+        <v>4</v>
+      </c>
+      <c r="G9" s="45"/>
+      <c r="H9" s="47"/>
+      <c r="I9" s="47"/>
+      <c r="J9" s="48"/>
+    </row>
+    <row r="10" spans="1:10" ht="15">
+      <c r="A10" s="40"/>
+      <c r="B10" s="40"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="40"/>
+      <c r="I10" s="40"/>
+      <c r="J10" s="40"/>
+    </row>
+    <row r="11" spans="1:10" ht="25.5">
+      <c r="A11" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="49" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" s="66"/>
+      <c r="D11" s="66"/>
+      <c r="E11" s="66"/>
+      <c r="F11" s="66"/>
+      <c r="G11" s="66"/>
+      <c r="H11" s="66"/>
+      <c r="I11" s="66"/>
+      <c r="J11" s="66"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="33"/>
+      <c r="B12" s="51" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="66"/>
+      <c r="D12" s="66"/>
+      <c r="E12" s="66"/>
+      <c r="F12" s="66"/>
+      <c r="G12" s="66"/>
+      <c r="H12" s="66"/>
+      <c r="I12" s="66"/>
+      <c r="J12" s="66"/>
+    </row>
+    <row r="13" spans="1:10" ht="13.5" thickBot="1">
+      <c r="A13" s="24"/>
+      <c r="B13" s="24"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="24"/>
+      <c r="H13" s="24"/>
+      <c r="I13" s="24"/>
+      <c r="J13" s="24"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="53"/>
+      <c r="D14" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" s="53"/>
+      <c r="F14" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G14" s="54"/>
+      <c r="H14" s="53"/>
+      <c r="I14" s="52" t="s">
+        <v>29</v>
+      </c>
+      <c r="J14" s="55"/>
+    </row>
+    <row r="15" spans="1:10" ht="111.75" customHeight="1">
+      <c r="A15" s="26">
+        <v>1</v>
+      </c>
+      <c r="B15" s="41" t="s">
+        <v>77</v>
+      </c>
+      <c r="C15" s="43"/>
+      <c r="D15" s="41" t="s">
+        <v>78</v>
+      </c>
+      <c r="E15" s="43"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="42"/>
+      <c r="H15" s="43"/>
+      <c r="I15" s="41"/>
+      <c r="J15" s="44"/>
+    </row>
+    <row r="16" spans="1:10" ht="29.25" customHeight="1">
+      <c r="A16" s="26">
+        <v>2</v>
+      </c>
+      <c r="B16" s="41" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" s="43"/>
+      <c r="D16" s="41" t="s">
+        <v>79</v>
+      </c>
+      <c r="E16" s="43"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="42"/>
+      <c r="H16" s="43"/>
+      <c r="I16" s="41"/>
+      <c r="J16" s="44"/>
+    </row>
+    <row r="17" spans="1:10" ht="27" customHeight="1">
+      <c r="A17" s="26">
+        <v>3</v>
+      </c>
+      <c r="B17" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" s="43"/>
+      <c r="D17" s="41" t="s">
+        <v>80</v>
+      </c>
+      <c r="E17" s="43"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="42"/>
+      <c r="H17" s="43"/>
+      <c r="I17" s="41"/>
+      <c r="J17" s="44"/>
+    </row>
+    <row r="18" spans="1:10" ht="33.75" customHeight="1">
+      <c r="A18" s="26">
+        <v>4</v>
+      </c>
+      <c r="B18" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="C18" s="43"/>
+      <c r="D18" s="41" t="s">
+        <v>81</v>
+      </c>
+      <c r="E18" s="43"/>
+      <c r="F18" s="41"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="43"/>
+      <c r="I18" s="41"/>
+      <c r="J18" s="44"/>
+    </row>
+    <row r="19" spans="1:10" ht="27" customHeight="1">
+      <c r="A19" s="26">
+        <v>5</v>
+      </c>
+      <c r="B19" s="41" t="s">
+        <v>56</v>
+      </c>
+      <c r="C19" s="43"/>
+      <c r="D19" s="41" t="s">
+        <v>80</v>
+      </c>
+      <c r="E19" s="43"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="42"/>
+      <c r="H19" s="43"/>
+      <c r="I19" s="41"/>
+      <c r="J19" s="44"/>
+    </row>
+    <row r="20" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A20" s="26">
+        <v>6</v>
+      </c>
+      <c r="B20" s="41" t="s">
+        <v>55</v>
+      </c>
+      <c r="C20" s="43"/>
+      <c r="D20" s="41" t="s">
+        <v>82</v>
+      </c>
+      <c r="E20" s="43"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="42"/>
+      <c r="H20" s="43"/>
+      <c r="I20" s="41"/>
+      <c r="J20" s="44"/>
+    </row>
+    <row r="21" spans="1:10" ht="21.75" customHeight="1">
+      <c r="A21" s="26">
+        <v>7</v>
+      </c>
+      <c r="B21" s="41" t="s">
+        <v>60</v>
+      </c>
+      <c r="C21" s="43"/>
+      <c r="D21" s="41" t="s">
+        <v>83</v>
+      </c>
+      <c r="E21" s="43"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="42"/>
+      <c r="H21" s="43"/>
+      <c r="I21" s="41"/>
+      <c r="J21" s="44"/>
+    </row>
+    <row r="22" spans="1:10" ht="32.25" customHeight="1">
+      <c r="A22" s="26">
+        <v>8</v>
+      </c>
+      <c r="B22" s="41" t="s">
+        <v>62</v>
+      </c>
+      <c r="C22" s="43"/>
+      <c r="D22" s="41" t="s">
+        <v>84</v>
+      </c>
+      <c r="E22" s="43"/>
+      <c r="F22" s="41"/>
+      <c r="G22" s="42"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="41"/>
+      <c r="J22" s="44"/>
+    </row>
+    <row r="23" spans="1:10" hidden="1">
+      <c r="A23" s="67" t="s">
+        <v>51</v>
+      </c>
+      <c r="B23" s="41"/>
+      <c r="C23" s="43"/>
+      <c r="D23" s="41"/>
+      <c r="E23" s="43"/>
+      <c r="F23" s="41"/>
+      <c r="G23" s="42"/>
+      <c r="H23" s="43"/>
+      <c r="I23" s="41"/>
+      <c r="J23" s="44"/>
+    </row>
+    <row r="24" spans="1:10" ht="22.5" customHeight="1">
+      <c r="A24" s="26">
+        <v>9</v>
+      </c>
+      <c r="B24" s="41" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24" s="43"/>
+      <c r="D24" s="41" t="s">
+        <v>85</v>
+      </c>
+      <c r="E24" s="43"/>
+      <c r="F24" s="41"/>
+      <c r="G24" s="42"/>
+      <c r="H24" s="43"/>
+      <c r="I24" s="41"/>
+      <c r="J24" s="44"/>
+    </row>
+    <row r="25" spans="1:10" ht="22.5" customHeight="1">
+      <c r="A25" s="26">
+        <v>10</v>
+      </c>
+      <c r="B25" s="41" t="s">
+        <v>63</v>
+      </c>
+      <c r="C25" s="43"/>
+      <c r="D25" s="41" t="s">
+        <v>86</v>
+      </c>
+      <c r="E25" s="43"/>
+      <c r="F25" s="41"/>
+      <c r="G25" s="42"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="41"/>
+      <c r="J25" s="44"/>
+    </row>
+    <row r="26" spans="1:10" ht="32.25" customHeight="1">
+      <c r="A26" s="26">
+        <v>11</v>
+      </c>
+      <c r="B26" s="41" t="s">
+        <v>64</v>
+      </c>
+      <c r="C26" s="43"/>
+      <c r="D26" s="41" t="s">
         <v>87</v>
       </c>
-      <c r="C6" s="41"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="18">
-        <v>1</v>
+      <c r="E26" s="43"/>
+      <c r="F26" s="41"/>
+      <c r="G26" s="42"/>
+      <c r="H26" s="43"/>
+      <c r="I26" s="41"/>
+      <c r="J26" s="44"/>
+    </row>
+    <row r="27" spans="1:10" ht="34.5" customHeight="1">
+      <c r="A27" s="26">
+        <v>12</v>
       </c>
-      <c r="G6" s="73" t="s">
-        <v>48</v>
+      <c r="B27" s="41" t="s">
+        <v>65</v>
       </c>
-      <c r="H6" s="41"/>
-      <c r="I6" s="41"/>
-      <c r="J6" s="43"/>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="28">
-        <v>2</v>
-      </c>
-      <c r="B7" s="40" t="s">
+      <c r="C27" s="43"/>
+      <c r="D27" s="41" t="s">
         <v>88</v>
       </c>
-      <c r="C7" s="41"/>
-      <c r="D7" s="42"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="18">
-        <v>2</v>
+      <c r="E27" s="43"/>
+      <c r="F27" s="41"/>
+      <c r="G27" s="42"/>
+      <c r="H27" s="43"/>
+      <c r="I27" s="41"/>
+      <c r="J27" s="44"/>
+    </row>
+    <row r="28" spans="1:10" ht="33" customHeight="1">
+      <c r="A28" s="26">
+        <v>13</v>
       </c>
-      <c r="G7" s="73" t="s">
-        <v>48</v>
+      <c r="B28" s="41" t="s">
+        <v>66</v>
       </c>
-      <c r="H7" s="41"/>
-      <c r="I7" s="41"/>
-      <c r="J7" s="43"/>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="28">
-        <v>3</v>
-      </c>
-      <c r="B8" s="40"/>
-      <c r="C8" s="41"/>
-      <c r="D8" s="42"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="18">
-        <v>3</v>
-      </c>
-      <c r="G8" s="40"/>
-      <c r="H8" s="41"/>
-      <c r="I8" s="41"/>
-      <c r="J8" s="43"/>
-    </row>
-    <row r="9" spans="1:10" ht="13.5" thickBot="1">
-      <c r="A9" s="29">
-        <v>4</v>
-      </c>
-      <c r="B9" s="44"/>
-      <c r="C9" s="46"/>
-      <c r="D9" s="45"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="21">
-        <v>4</v>
-      </c>
-      <c r="G9" s="44"/>
-      <c r="H9" s="46"/>
-      <c r="I9" s="46"/>
-      <c r="J9" s="47"/>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="25"/>
-      <c r="B10" s="25"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="25"/>
-      <c r="H10" s="25"/>
-      <c r="I10" s="25"/>
-      <c r="J10" s="25"/>
-    </row>
-    <row r="11" spans="1:10" ht="25.5">
-      <c r="A11" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" s="48" t="s">
-        <v>56</v>
-      </c>
-      <c r="C11" s="49"/>
-      <c r="D11" s="49"/>
-      <c r="E11" s="49"/>
-      <c r="F11" s="49"/>
-      <c r="G11" s="49"/>
-      <c r="H11" s="49"/>
-      <c r="I11" s="49"/>
-      <c r="J11" s="49"/>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="26"/>
-      <c r="B12" s="72" t="s">
-        <v>48</v>
-      </c>
-      <c r="C12" s="49"/>
-      <c r="D12" s="49"/>
-      <c r="E12" s="49"/>
-      <c r="F12" s="49"/>
-      <c r="G12" s="49"/>
-      <c r="H12" s="49"/>
-      <c r="I12" s="49"/>
-      <c r="J12" s="49"/>
-    </row>
-    <row r="13" spans="1:10" ht="13.5" thickBot="1">
-      <c r="A13" s="26"/>
-      <c r="B13" s="26"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="26"/>
-      <c r="G13" s="26"/>
-      <c r="H13" s="26"/>
-      <c r="I13" s="26"/>
-      <c r="J13" s="26"/>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" s="52"/>
-      <c r="D14" s="51" t="s">
-        <v>27</v>
-      </c>
-      <c r="E14" s="52"/>
-      <c r="F14" s="51" t="s">
-        <v>28</v>
-      </c>
-      <c r="G14" s="53"/>
-      <c r="H14" s="52"/>
-      <c r="I14" s="51" t="s">
-        <v>29</v>
-      </c>
-      <c r="J14" s="54"/>
-    </row>
-    <row r="15" spans="1:10" ht="111.75" customHeight="1">
-      <c r="A15" s="28">
-        <v>1</v>
-      </c>
-      <c r="B15" s="40" t="s">
-        <v>54</v>
-      </c>
-      <c r="C15" s="42"/>
-      <c r="D15" s="40" t="s">
+      <c r="C28" s="43"/>
+      <c r="D28" s="41" t="s">
         <v>89</v>
       </c>
-      <c r="E15" s="42"/>
-      <c r="F15" s="40"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="42"/>
-      <c r="I15" s="40"/>
-      <c r="J15" s="43"/>
-    </row>
-    <row r="16" spans="1:10" ht="29.25" customHeight="1">
-      <c r="A16" s="28">
-        <v>2</v>
+      <c r="E28" s="43"/>
+      <c r="F28" s="68"/>
+      <c r="G28" s="69"/>
+      <c r="H28" s="70"/>
+      <c r="I28" s="41"/>
+      <c r="J28" s="44"/>
+    </row>
+    <row r="29" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A29" s="26">
+        <v>14</v>
       </c>
-      <c r="B16" s="40" t="s">
-        <v>63</v>
-      </c>
-      <c r="C16" s="42"/>
-      <c r="D16" s="40" t="s">
-        <v>55</v>
-      </c>
-      <c r="E16" s="42"/>
-      <c r="F16" s="40"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="42"/>
-      <c r="I16" s="40"/>
-      <c r="J16" s="43"/>
-    </row>
-    <row r="17" spans="1:10" ht="27" customHeight="1">
-      <c r="A17" s="28">
-        <v>3</v>
-      </c>
-      <c r="B17" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="C17" s="42"/>
-      <c r="D17" s="40" t="s">
-        <v>57</v>
-      </c>
-      <c r="E17" s="42"/>
-      <c r="F17" s="40"/>
-      <c r="G17" s="41"/>
-      <c r="H17" s="42"/>
-      <c r="I17" s="40"/>
-      <c r="J17" s="43"/>
-    </row>
-    <row r="18" spans="1:10" ht="33.75" customHeight="1">
-      <c r="A18" s="28">
-        <v>4</v>
-      </c>
-      <c r="B18" s="40" t="s">
-        <v>61</v>
-      </c>
-      <c r="C18" s="42"/>
-      <c r="D18" s="40" t="s">
-        <v>58</v>
-      </c>
-      <c r="E18" s="42"/>
-      <c r="F18" s="40"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="42"/>
-      <c r="I18" s="40"/>
-      <c r="J18" s="43"/>
-    </row>
-    <row r="19" spans="1:10" ht="27" customHeight="1">
-      <c r="A19" s="28">
-        <v>5</v>
-      </c>
-      <c r="B19" s="40" t="s">
-        <v>60</v>
-      </c>
-      <c r="C19" s="42"/>
-      <c r="D19" s="40" t="s">
-        <v>57</v>
-      </c>
-      <c r="E19" s="42"/>
-      <c r="F19" s="40"/>
-      <c r="G19" s="41"/>
-      <c r="H19" s="42"/>
-      <c r="I19" s="40"/>
-      <c r="J19" s="43"/>
-    </row>
-    <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="28">
-        <v>6</v>
-      </c>
-      <c r="B20" s="40" t="s">
-        <v>59</v>
-      </c>
-      <c r="C20" s="42"/>
-      <c r="D20" s="40" t="s">
-        <v>64</v>
-      </c>
-      <c r="E20" s="42"/>
-      <c r="F20" s="40"/>
-      <c r="G20" s="41"/>
-      <c r="H20" s="42"/>
-      <c r="I20" s="40"/>
-      <c r="J20" s="43"/>
-    </row>
-    <row r="21" spans="1:10" ht="21.75" customHeight="1">
-      <c r="A21" s="28">
-        <v>7</v>
-      </c>
-      <c r="B21" s="40" t="s">
-        <v>65</v>
-      </c>
-      <c r="C21" s="42"/>
-      <c r="D21" s="40" t="s">
+      <c r="B29" s="41" t="s">
         <v>67</v>
       </c>
-      <c r="E21" s="42"/>
-      <c r="F21" s="40"/>
-      <c r="G21" s="41"/>
-      <c r="H21" s="42"/>
-      <c r="I21" s="40"/>
-      <c r="J21" s="43"/>
-    </row>
-    <row r="22" spans="1:10" ht="27" customHeight="1">
-      <c r="A22" s="28">
-        <v>8</v>
+      <c r="C29" s="43"/>
+      <c r="D29" s="41" t="s">
+        <v>90</v>
       </c>
-      <c r="B22" s="40" t="s">
+      <c r="E29" s="42"/>
+      <c r="F29" s="71"/>
+      <c r="G29" s="72"/>
+      <c r="H29" s="72"/>
+      <c r="I29" s="73"/>
+      <c r="J29" s="44"/>
+    </row>
+    <row r="30" spans="1:10" ht="24.75" customHeight="1">
+      <c r="A30" s="26">
+        <v>15</v>
+      </c>
+      <c r="B30" s="41" t="s">
+        <v>68</v>
+      </c>
+      <c r="C30" s="43"/>
+      <c r="D30" s="41" t="s">
+        <v>91</v>
+      </c>
+      <c r="E30" s="42"/>
+      <c r="F30" s="71"/>
+      <c r="G30" s="72"/>
+      <c r="H30" s="72"/>
+      <c r="I30" s="73"/>
+      <c r="J30" s="44"/>
+    </row>
+    <row r="31" spans="1:10" ht="30.75" customHeight="1">
+      <c r="A31" s="26">
+        <v>16</v>
+      </c>
+      <c r="B31" s="41" t="s">
         <v>69</v>
       </c>
-      <c r="C22" s="42"/>
-      <c r="D22" s="40" t="s">
-        <v>68</v>
+      <c r="C31" s="43"/>
+      <c r="D31" s="41" t="s">
+        <v>88</v>
       </c>
-      <c r="E22" s="42"/>
-      <c r="F22" s="40"/>
-      <c r="G22" s="41"/>
-      <c r="H22" s="42"/>
-      <c r="I22" s="40"/>
-      <c r="J22" s="43"/>
-    </row>
-    <row r="23" spans="1:10" hidden="1">
-      <c r="A23" s="34" t="s">
-        <v>51</v>
+      <c r="E31" s="42"/>
+      <c r="F31" s="71"/>
+      <c r="G31" s="72"/>
+      <c r="H31" s="72"/>
+      <c r="I31" s="73"/>
+      <c r="J31" s="44"/>
+    </row>
+    <row r="32" spans="1:10" ht="33" customHeight="1">
+      <c r="A32" s="26">
+        <v>17</v>
       </c>
-      <c r="B23" s="40"/>
-      <c r="C23" s="42"/>
-      <c r="D23" s="40"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="40"/>
-      <c r="G23" s="41"/>
-      <c r="H23" s="42"/>
-      <c r="I23" s="40"/>
-      <c r="J23" s="43"/>
-    </row>
-    <row r="24" spans="1:10" ht="22.5" customHeight="1">
-      <c r="A24" s="28">
-        <v>9</v>
-      </c>
-      <c r="B24" s="40" t="s">
-        <v>66</v>
-      </c>
-      <c r="C24" s="42"/>
-      <c r="D24" s="40" t="s">
+      <c r="B32" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="E24" s="42"/>
-      <c r="F24" s="40"/>
-      <c r="G24" s="41"/>
-      <c r="H24" s="42"/>
-      <c r="I24" s="40"/>
-      <c r="J24" s="43"/>
-    </row>
-    <row r="25" spans="1:10" ht="22.5" customHeight="1">
-      <c r="A25" s="28">
-        <v>10</v>
+      <c r="C32" s="43"/>
+      <c r="D32" s="41" t="s">
+        <v>92</v>
       </c>
-      <c r="B25" s="40" t="s">
+      <c r="E32" s="42"/>
+      <c r="F32" s="71"/>
+      <c r="G32" s="72"/>
+      <c r="H32" s="72"/>
+      <c r="I32" s="73"/>
+      <c r="J32" s="44"/>
+    </row>
+    <row r="33" spans="1:11" ht="31.5" customHeight="1">
+      <c r="A33" s="26">
+        <v>18</v>
+      </c>
+      <c r="B33" s="41" t="s">
+        <v>73</v>
+      </c>
+      <c r="C33" s="43"/>
+      <c r="D33" s="41" t="s">
+        <v>93</v>
+      </c>
+      <c r="E33" s="42"/>
+      <c r="F33" s="71"/>
+      <c r="G33" s="72"/>
+      <c r="H33" s="72"/>
+      <c r="I33" s="73"/>
+      <c r="J33" s="44"/>
+    </row>
+    <row r="34" spans="1:11" ht="27" customHeight="1">
+      <c r="A34" s="74">
+        <v>19</v>
+      </c>
+      <c r="B34" s="68" t="s">
         <v>71</v>
       </c>
-      <c r="C25" s="42"/>
-      <c r="D25" s="40" t="s">
-        <v>90</v>
+      <c r="C34" s="70"/>
+      <c r="D34" s="68" t="s">
+        <v>94</v>
       </c>
-      <c r="E25" s="42"/>
-      <c r="F25" s="40"/>
-      <c r="G25" s="41"/>
-      <c r="H25" s="42"/>
-      <c r="I25" s="40"/>
-      <c r="J25" s="43"/>
-    </row>
-    <row r="26" spans="1:10" ht="29.25" customHeight="1">
-      <c r="A26" s="28">
-        <v>11</v>
+      <c r="E34" s="69"/>
+      <c r="F34" s="75"/>
+      <c r="G34" s="76"/>
+      <c r="H34" s="76"/>
+      <c r="I34" s="77"/>
+      <c r="J34" s="78"/>
+    </row>
+    <row r="35" spans="1:11" ht="23.25" customHeight="1">
+      <c r="A35" s="79">
+        <v>20</v>
       </c>
-      <c r="B26" s="40" t="s">
+      <c r="B35" s="71" t="s">
         <v>72</v>
       </c>
-      <c r="C26" s="42"/>
-      <c r="D26" s="40" t="s">
-        <v>73</v>
-      </c>
-      <c r="E26" s="42"/>
-      <c r="F26" s="40"/>
-      <c r="G26" s="41"/>
-      <c r="H26" s="42"/>
-      <c r="I26" s="40"/>
-      <c r="J26" s="43"/>
-    </row>
-    <row r="27" spans="1:10" ht="34.5" customHeight="1">
-      <c r="A27" s="28">
-        <v>12</v>
-      </c>
-      <c r="B27" s="40" t="s">
-        <v>74</v>
-      </c>
-      <c r="C27" s="42"/>
-      <c r="D27" s="40" t="s">
-        <v>91</v>
-      </c>
-      <c r="E27" s="42"/>
-      <c r="F27" s="40"/>
-      <c r="G27" s="41"/>
-      <c r="H27" s="42"/>
-      <c r="I27" s="40"/>
-      <c r="J27" s="43"/>
-    </row>
-    <row r="28" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A28" s="28">
-        <v>13</v>
-      </c>
-      <c r="B28" s="40" t="s">
-        <v>75</v>
-      </c>
-      <c r="C28" s="42"/>
-      <c r="D28" s="40" t="s">
-        <v>76</v>
-      </c>
-      <c r="E28" s="42"/>
-      <c r="F28" s="62"/>
-      <c r="G28" s="64"/>
-      <c r="H28" s="63"/>
-      <c r="I28" s="40"/>
-      <c r="J28" s="43"/>
-    </row>
-    <row r="29" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A29" s="28">
-        <v>14</v>
-      </c>
-      <c r="B29" s="40" t="s">
-        <v>77</v>
-      </c>
-      <c r="C29" s="42"/>
-      <c r="D29" s="40" t="s">
-        <v>78</v>
-      </c>
-      <c r="E29" s="41"/>
-      <c r="F29" s="69"/>
-      <c r="G29" s="70"/>
-      <c r="H29" s="70"/>
-      <c r="I29" s="71"/>
-      <c r="J29" s="43"/>
-    </row>
-    <row r="30" spans="1:10" ht="24.75" customHeight="1">
-      <c r="A30" s="28">
-        <v>15</v>
-      </c>
-      <c r="B30" s="40" t="s">
-        <v>79</v>
-      </c>
-      <c r="C30" s="42"/>
-      <c r="D30" s="40" t="s">
-        <v>92</v>
-      </c>
-      <c r="E30" s="41"/>
-      <c r="F30" s="69"/>
-      <c r="G30" s="70"/>
-      <c r="H30" s="70"/>
-      <c r="I30" s="71"/>
-      <c r="J30" s="43"/>
-    </row>
-    <row r="31" spans="1:10" ht="27" customHeight="1">
-      <c r="A31" s="28">
-        <v>16</v>
-      </c>
-      <c r="B31" s="40" t="s">
-        <v>80</v>
-      </c>
-      <c r="C31" s="42"/>
-      <c r="D31" s="40" t="s">
-        <v>81</v>
-      </c>
-      <c r="E31" s="41"/>
-      <c r="F31" s="69"/>
-      <c r="G31" s="70"/>
-      <c r="H31" s="70"/>
-      <c r="I31" s="71"/>
-      <c r="J31" s="43"/>
-    </row>
-    <row r="32" spans="1:10" ht="27" customHeight="1">
-      <c r="A32" s="28">
-        <v>17</v>
-      </c>
-      <c r="B32" s="40" t="s">
-        <v>82</v>
-      </c>
-      <c r="C32" s="42"/>
-      <c r="D32" s="40" t="s">
-        <v>93</v>
-      </c>
-      <c r="E32" s="41"/>
-      <c r="F32" s="69"/>
-      <c r="G32" s="70"/>
-      <c r="H32" s="70"/>
-      <c r="I32" s="71"/>
-      <c r="J32" s="43"/>
-    </row>
-    <row r="33" spans="1:11" ht="27" customHeight="1">
-      <c r="A33" s="28">
-        <v>18</v>
-      </c>
-      <c r="B33" s="40" t="s">
-        <v>85</v>
-      </c>
-      <c r="C33" s="42"/>
-      <c r="D33" s="40" t="s">
-        <v>94</v>
-      </c>
-      <c r="E33" s="41"/>
-      <c r="F33" s="69"/>
-      <c r="G33" s="70"/>
-      <c r="H33" s="70"/>
-      <c r="I33" s="71"/>
-      <c r="J33" s="43"/>
-    </row>
-    <row r="34" spans="1:11" ht="27" customHeight="1">
-      <c r="A34" s="36">
-        <v>19</v>
-      </c>
-      <c r="B34" s="62" t="s">
-        <v>83</v>
-      </c>
-      <c r="C34" s="63"/>
-      <c r="D34" s="62" t="s">
+      <c r="C35" s="72"/>
+      <c r="D35" s="71" t="s">
         <v>95</v>
       </c>
-      <c r="E34" s="64"/>
-      <c r="F34" s="65"/>
-      <c r="G34" s="66"/>
-      <c r="H34" s="66"/>
-      <c r="I34" s="67"/>
-      <c r="J34" s="68"/>
-    </row>
-    <row r="35" spans="1:11" ht="23.25" customHeight="1">
-      <c r="A35" s="39">
-        <v>20</v>
-      </c>
-      <c r="B35" s="69" t="s">
-        <v>84</v>
-      </c>
-      <c r="C35" s="70"/>
-      <c r="D35" s="69" t="s">
-        <v>86</v>
-      </c>
-      <c r="E35" s="70"/>
-      <c r="F35" s="69"/>
-      <c r="G35" s="70"/>
-      <c r="H35" s="70"/>
-      <c r="I35" s="69"/>
-      <c r="J35" s="70"/>
-    </row>
-    <row r="36" spans="1:11" s="33" customFormat="1" ht="23.25" customHeight="1">
-      <c r="A36" s="38"/>
-      <c r="B36" s="77"/>
-      <c r="C36" s="76"/>
-      <c r="D36" s="75"/>
-      <c r="E36" s="76"/>
-      <c r="F36" s="35"/>
-      <c r="G36" s="35"/>
-      <c r="H36" s="35"/>
-      <c r="I36" s="35"/>
-      <c r="J36" s="35"/>
-    </row>
-    <row r="37" spans="1:11" s="33" customFormat="1" ht="23.25" customHeight="1">
-      <c r="A37" s="35"/>
-      <c r="B37" s="35"/>
-      <c r="C37" s="35"/>
-      <c r="D37" s="75"/>
-      <c r="E37" s="76"/>
-      <c r="F37" s="77"/>
-      <c r="G37" s="76"/>
-      <c r="H37" s="76"/>
-      <c r="I37" s="77"/>
-      <c r="J37" s="76"/>
-      <c r="K37" s="35"/>
+      <c r="E35" s="72"/>
+      <c r="F35" s="71"/>
+      <c r="G35" s="72"/>
+      <c r="H35" s="72"/>
+      <c r="I35" s="71"/>
+      <c r="J35" s="72"/>
+    </row>
+    <row r="36" spans="1:11" s="28" customFormat="1" ht="23.25" customHeight="1">
+      <c r="A36" s="31"/>
+      <c r="B36" s="65"/>
+      <c r="C36" s="64"/>
+      <c r="D36" s="63"/>
+      <c r="E36" s="64"/>
+      <c r="F36" s="29"/>
+      <c r="G36" s="29"/>
+      <c r="H36" s="29"/>
+      <c r="I36" s="29"/>
+      <c r="J36" s="29"/>
+    </row>
+    <row r="37" spans="1:11" s="28" customFormat="1" ht="23.25" customHeight="1">
+      <c r="A37" s="29"/>
+      <c r="B37" s="29"/>
+      <c r="C37" s="29"/>
+      <c r="D37" s="63"/>
+      <c r="E37" s="64"/>
+      <c r="F37" s="65"/>
+      <c r="G37" s="64"/>
+      <c r="H37" s="64"/>
+      <c r="I37" s="65"/>
+      <c r="J37" s="64"/>
+      <c r="K37" s="29"/>
     </row>
     <row r="38" spans="1:11">
-      <c r="A38" s="37"/>
-      <c r="B38" s="37"/>
-      <c r="C38" s="37"/>
-      <c r="D38" s="37"/>
-      <c r="E38" s="37"/>
-      <c r="F38" s="37"/>
-      <c r="G38" s="37"/>
-      <c r="H38" s="37"/>
-      <c r="I38" s="37"/>
-      <c r="J38" s="37"/>
-      <c r="K38" s="35"/>
+      <c r="A38" s="30"/>
+      <c r="B38" s="30"/>
+      <c r="C38" s="30"/>
+      <c r="D38" s="30"/>
+      <c r="E38" s="30"/>
+      <c r="F38" s="30"/>
+      <c r="G38" s="30"/>
+      <c r="H38" s="30"/>
+      <c r="I38" s="30"/>
+      <c r="J38" s="30"/>
+      <c r="K38" s="29"/>
     </row>
     <row r="39" spans="1:11">
-      <c r="A39" s="26"/>
-      <c r="B39" s="26"/>
-      <c r="C39" s="26"/>
-      <c r="D39" s="26"/>
-      <c r="E39" s="26"/>
-      <c r="F39" s="26"/>
-      <c r="G39" s="26"/>
-      <c r="H39" s="26"/>
-      <c r="I39" s="26"/>
-      <c r="J39" s="26"/>
+      <c r="A39" s="24"/>
+      <c r="B39" s="24"/>
+      <c r="C39" s="24"/>
+      <c r="D39" s="24"/>
+      <c r="E39" s="24"/>
+      <c r="F39" s="24"/>
+      <c r="G39" s="24"/>
+      <c r="H39" s="24"/>
+      <c r="I39" s="24"/>
+      <c r="J39" s="24"/>
     </row>
     <row r="40" spans="1:11">
-      <c r="A40" s="26"/>
-      <c r="B40" s="26"/>
-      <c r="C40" s="26"/>
-      <c r="D40" s="26"/>
-      <c r="E40" s="26"/>
-      <c r="F40" s="26"/>
-      <c r="G40" s="26"/>
-      <c r="H40" s="26"/>
-      <c r="I40" s="26"/>
-      <c r="J40" s="26"/>
+      <c r="A40" s="24"/>
+      <c r="B40" s="24"/>
+      <c r="C40" s="24"/>
+      <c r="D40" s="24"/>
+      <c r="E40" s="24"/>
+      <c r="F40" s="24"/>
+      <c r="G40" s="24"/>
+      <c r="H40" s="24"/>
+      <c r="I40" s="24"/>
+      <c r="J40" s="24"/>
     </row>
     <row r="41" spans="1:11">
-      <c r="A41" s="26"/>
-      <c r="B41" s="26"/>
-      <c r="C41" s="26"/>
-      <c r="D41" s="26"/>
-      <c r="E41" s="26"/>
-      <c r="F41" s="26"/>
-      <c r="G41" s="26"/>
-      <c r="H41" s="26"/>
-      <c r="I41" s="26"/>
-      <c r="J41" s="26"/>
+      <c r="A41" s="24"/>
+      <c r="B41" s="24"/>
+      <c r="C41" s="24"/>
+      <c r="D41" s="24"/>
+      <c r="E41" s="24"/>
+      <c r="F41" s="24"/>
+      <c r="G41" s="24"/>
+      <c r="H41" s="24"/>
+      <c r="I41" s="24"/>
+      <c r="J41" s="24"/>
     </row>
     <row r="42" spans="1:11">
-      <c r="A42" s="26"/>
-      <c r="B42" s="26"/>
-      <c r="C42" s="26"/>
-      <c r="D42" s="26"/>
-      <c r="E42" s="26"/>
-      <c r="F42" s="26"/>
-      <c r="G42" s="26"/>
-      <c r="H42" s="26"/>
-      <c r="I42" s="26"/>
-      <c r="J42" s="26"/>
+      <c r="A42" s="24"/>
+      <c r="B42" s="24"/>
+      <c r="C42" s="24"/>
+      <c r="D42" s="24"/>
+      <c r="E42" s="24"/>
+      <c r="F42" s="24"/>
+      <c r="G42" s="24"/>
+      <c r="H42" s="24"/>
+      <c r="I42" s="24"/>
+      <c r="J42" s="24"/>
     </row>
     <row r="43" spans="1:11">
-      <c r="A43" s="26"/>
-      <c r="B43" s="26"/>
-      <c r="C43" s="26"/>
-      <c r="D43" s="26"/>
-      <c r="E43" s="26"/>
-      <c r="F43" s="26"/>
-      <c r="G43" s="26"/>
-      <c r="H43" s="26"/>
-      <c r="I43" s="26"/>
-      <c r="J43" s="26"/>
+      <c r="A43" s="24"/>
+      <c r="B43" s="24"/>
+      <c r="C43" s="24"/>
+      <c r="D43" s="24"/>
+      <c r="E43" s="24"/>
+      <c r="F43" s="24"/>
+      <c r="G43" s="24"/>
+      <c r="H43" s="24"/>
+      <c r="I43" s="24"/>
+      <c r="J43" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="113">
